--- a/Dhamil28_2/Assignment 2.xlsx
+++ b/Dhamil28_2/Assignment 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/14d45f3f938d389f/Documents/GitHub/64018_-Dhamil28/Dhamil28_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{CC38EFD1-8FDF-47E9-8D53-2AEEB32A28DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77171D7-6450-4F0D-B804-8B4FEC29CD93}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{CC38EFD1-8FDF-47E9-8D53-2AEEB32A28DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0208A548-48BC-4115-88DA-4BFF8469851B}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{BE2B597D-B120-4C36-9BAF-3210B7FB0B94}"/>
   </bookViews>
@@ -921,7 +921,7 @@
       <c r="F8" s="4">
         <v>420</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <f>E8*F8</f>
         <v>223440</v>
       </c>
@@ -958,7 +958,7 @@
       <c r="F9" s="4">
         <v>360</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <f t="shared" ref="G9:G10" si="1">E9*F9</f>
         <v>307080</v>
       </c>
@@ -995,7 +995,7 @@
       <c r="F10" s="4">
         <v>300</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <f t="shared" si="1"/>
         <v>164100</v>
       </c>
